--- a/arquivos/formulario_expandido.xlsx
+++ b/arquivos/formulario_expandido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VALEMAIS PROMOTORA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28235261-58E6-4DE0-A01C-562A13EA1494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48711E67-A53A-4F3C-9CE0-6E99590CCC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="152">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -473,6 +473,9 @@
   </si>
   <si>
     <t>sem opnião</t>
+  </si>
+  <si>
+    <t>Na sua opinião, é justo que, ao "comprar" um jogo digital, o usuário tenha apenas uma licença de uso?</t>
   </si>
 </sst>
 </file>
@@ -821,6 +824,9 @@
   <dimension ref="A1:M151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="3" max="3" width="38.5546875" customWidth="1"/>
+    <col min="4" max="4" width="29.21875" customWidth="1"/>
+    <col min="12" max="12" width="28.33203125" customWidth="1"/>
     <col min="13" max="13" width="88.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -862,7 +868,7 @@
         <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
